--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/sep-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/sep-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC sep-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC sep-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17080,7 +17080,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17812,7 +17812,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19337,7 +19337,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19459,7 +19459,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20557,7 +20557,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20679,7 +20679,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21045,7 +21045,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22265,7 +22265,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22448,7 +22448,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23851,7 +23851,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24034,7 +24034,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24583,7 +24583,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24888,7 +24888,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -25925,7 +25925,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -25986,7 +25986,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26352,7 +26352,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -26657,7 +26657,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27450,7 +27450,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27572,7 +27572,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -27816,7 +27816,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -27938,7 +27938,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28121,7 +28121,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28182,7 +28182,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28243,7 +28243,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28304,7 +28304,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -28426,7 +28426,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28487,7 +28487,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28609,7 +28609,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28670,7 +28670,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28731,7 +28731,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -28975,7 +28975,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29036,7 +29036,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29097,7 +29097,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29219,7 +29219,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29402,7 +29402,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29585,7 +29585,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29768,7 +29768,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -29829,7 +29829,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -29951,7 +29951,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30012,7 +30012,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30073,7 +30073,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30195,7 +30195,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30317,7 +30317,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -30378,7 +30378,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30683,7 +30683,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -30927,7 +30927,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31171,7 +31171,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31232,7 +31232,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31293,7 +31293,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31354,7 +31354,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31415,7 +31415,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31476,7 +31476,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31598,7 +31598,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31659,7 +31659,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31720,7 +31720,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31781,7 +31781,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -31842,7 +31842,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31903,7 +31903,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32025,7 +32025,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32086,7 +32086,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32147,7 +32147,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32269,7 +32269,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32330,7 +32330,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32452,7 +32452,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32513,7 +32513,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -32635,7 +32635,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -32696,7 +32696,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32757,7 +32757,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32879,7 +32879,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33001,7 +33001,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33062,7 +33062,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -33123,7 +33123,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33184,7 +33184,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -33245,7 +33245,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33306,7 +33306,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -33367,7 +33367,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -33428,7 +33428,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33489,7 +33489,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -33550,7 +33550,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33611,7 +33611,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33672,7 +33672,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33733,7 +33733,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -33794,7 +33794,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -33855,7 +33855,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -33916,7 +33916,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -33977,7 +33977,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34038,7 +34038,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34160,7 +34160,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34221,7 +34221,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34282,7 +34282,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34404,7 +34404,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34465,7 +34465,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34587,7 +34587,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34648,7 +34648,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34709,7 +34709,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -34770,7 +34770,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -34831,7 +34831,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -34892,7 +34892,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -34953,7 +34953,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35075,7 +35075,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35136,7 +35136,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35197,7 +35197,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35258,7 +35258,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35319,7 +35319,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35380,7 +35380,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35441,7 +35441,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -35502,7 +35502,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35624,7 +35624,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35685,7 +35685,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -35929,7 +35929,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -35990,7 +35990,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36051,7 +36051,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36112,7 +36112,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36173,7 +36173,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36234,7 +36234,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -36295,7 +36295,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36356,7 +36356,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -36417,7 +36417,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36539,7 +36539,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -36600,7 +36600,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -36661,7 +36661,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -36783,7 +36783,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -36844,7 +36844,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -36905,7 +36905,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -36966,7 +36966,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37027,7 +37027,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -37088,7 +37088,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37149,7 +37149,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -37271,7 +37271,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37332,7 +37332,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37393,7 +37393,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -37454,7 +37454,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -37515,7 +37515,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -37576,7 +37576,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37637,7 +37637,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -37698,7 +37698,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -37759,7 +37759,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -37820,7 +37820,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -37881,7 +37881,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -37942,7 +37942,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38003,7 +38003,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -38064,7 +38064,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38125,7 +38125,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38247,7 +38247,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38308,7 +38308,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -38369,7 +38369,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -38430,7 +38430,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -38491,7 +38491,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38552,7 +38552,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -38674,7 +38674,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -38796,7 +38796,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -38857,7 +38857,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -38918,7 +38918,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -38979,7 +38979,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39040,7 +39040,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -39101,7 +39101,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39162,7 +39162,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39223,7 +39223,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -39284,7 +39284,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -39345,7 +39345,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39467,7 +39467,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39528,7 +39528,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -39589,7 +39589,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -39650,7 +39650,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -39711,7 +39711,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -39833,7 +39833,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -39894,7 +39894,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -39955,7 +39955,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -40016,7 +40016,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -40077,7 +40077,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -40138,7 +40138,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -40199,7 +40199,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -40260,7 +40260,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -40321,7 +40321,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -40382,7 +40382,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -40443,7 +40443,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -40504,7 +40504,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -40565,7 +40565,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40626,7 +40626,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40687,7 +40687,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -40748,7 +40748,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -40809,7 +40809,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -40870,7 +40870,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -40931,7 +40931,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -40992,7 +40992,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41053,7 +41053,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -41114,7 +41114,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -41175,7 +41175,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41236,7 +41236,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -41297,7 +41297,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -41358,7 +41358,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -41419,7 +41419,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -41480,7 +41480,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -41602,7 +41602,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -41663,7 +41663,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41724,7 +41724,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -41785,7 +41785,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41846,7 +41846,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41907,7 +41907,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -41968,7 +41968,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42029,7 +42029,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42090,7 +42090,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42151,7 +42151,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42212,7 +42212,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42273,7 +42273,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -42334,7 +42334,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42395,7 +42395,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/sep-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/sep-2025.xlsx
@@ -33779,7 +33779,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
@@ -34938,7 +34938,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/sep-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/sep-2025.xlsx
@@ -623,7 +623,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +810,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +875,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1257,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1444,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1570,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1635,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2005,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2070,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2135,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2261,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2448,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2513,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2578,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2643,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2708,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2773,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3391,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3517,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3582,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3647,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3895,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4147,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4273,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4399,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4464,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4529,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4716,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4842,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4907,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4972,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5037,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5102,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5411,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5537,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5663,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5728,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5854,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5919,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +5984,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6049,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6114,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6240,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6305,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6370,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6496,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6744,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6809,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7057,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7122,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7309,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7435,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7561,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7687,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7813,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7939,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8004,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8313,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8439,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8687,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8813,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8878,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9126,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9191,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9256,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9321,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9386,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9451,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9577,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9703,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9768,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9833,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10020,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10146,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10211,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10276,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10341,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10406,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10471,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10597,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10662,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10788,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10914,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +10979,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11166,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11231,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11296,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11483,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11548,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11796,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11861,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12048,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12113,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12178,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12243,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12369,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12434,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12560,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12625,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12690,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12755,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12942,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13190,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13255,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13320,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13385,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13450,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13515,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13580,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13645,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13771,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13897,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +13962,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14027,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14153,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14218,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14283,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14531,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14596,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14722,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14787,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14852,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15100,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15165,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15230,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15295,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15360,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15425,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15734,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16104,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16230,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16417,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16482,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16547,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16673,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16738,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +16803,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +16868,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +16933,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17303,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17734,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +17860,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +17986,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18051,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18299,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18364,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18429,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18555,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18620,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18685,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +18811,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +18876,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19063,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19128,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19193,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19258,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19323,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19388,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19514,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19579,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19644,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19709,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +19774,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +19839,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +19904,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +19969,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20034,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20160,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20225,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20290,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20355,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20664,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20729,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +20855,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +20920,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +20985,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21050,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21298,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21424,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21611,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +21798,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +21863,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +21928,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +21993,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22058,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22123,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22188,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22253,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22318,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22383,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22570,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22635,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +22761,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +22826,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +22891,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +22956,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23021,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23208,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23273,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23460,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +23525,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23651,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +23716,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +23781,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +23907,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +23972,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24159,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24224,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +24350,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +24476,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +24541,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +24789,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +24976,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25041,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25106,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25232,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25297,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +25362,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +25488,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25614,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +25740,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +25805,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +25870,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +25935,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26000,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26187,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26252,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +26378,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26565,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25755,7 +26691,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +26756,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +26821,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +26947,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27012,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27077,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27142,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +27207,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +27455,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +27520,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27585,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +27650,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +27715,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +27902,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28028,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28093,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28158,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28223,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +28349,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +28475,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +28784,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +28910,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29036,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29101,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +29166,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +29231,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +29296,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +29361,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +29426,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +29491,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +29617,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +29682,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +29808,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +29873,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +30060,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30125,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +30251,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29232,7 +30316,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +30381,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +30507,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +30633,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +30698,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +30763,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +30828,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +31503,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +31690,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +31816,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +31942,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +32007,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30940,7 +32072,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31001,7 +32137,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31062,7 +32202,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +32267,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31184,7 +32332,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +32397,11 @@
           <t>77.550.346-7</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31306,7 +32462,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31367,7 +32527,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +32592,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +32657,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +32783,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +32848,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +32974,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31855,7 +33039,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31916,7 +33104,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31977,7 +33169,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +33295,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +33360,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32221,7 +33425,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +33551,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32404,7 +33616,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +33681,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +33746,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32587,7 +33811,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32648,7 +33876,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32770,7 +34002,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32892,7 +34128,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33441,7 +34681,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33502,7 +34746,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33563,7 +34811,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33624,7 +34876,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33685,7 +34941,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33868,7 +35128,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34051,7 +35315,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34173,7 +35441,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34295,7 +35567,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34356,7 +35632,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34661,7 +35941,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34722,7 +36006,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34783,7 +36071,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34844,7 +36136,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35027,7 +36323,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35271,7 +36571,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35393,7 +36697,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35454,7 +36762,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35576,7 +36888,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35637,7 +36953,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35698,7 +37018,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35820,7 +37144,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35881,7 +37209,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36003,7 +37335,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36064,7 +37400,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36186,7 +37526,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36247,7 +37591,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36369,7 +37717,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36430,7 +37782,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36491,7 +37847,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36613,7 +37973,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36735,7 +38099,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36918,7 +38286,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36979,7 +38351,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37162,7 +38538,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37223,7 +38603,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37284,7 +38668,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37345,7 +38733,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37528,7 +38920,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37650,7 +39046,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37711,7 +39111,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37772,7 +39176,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37833,7 +39241,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37894,7 +39306,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37955,7 +39371,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38077,7 +39497,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38138,7 +39562,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38260,7 +39688,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38321,7 +39753,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38443,7 +39879,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38504,7 +39944,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38565,7 +40009,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38687,7 +40135,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38809,7 +40261,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38931,7 +40387,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38992,7 +40452,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39114,7 +40578,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39297,7 +40765,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39358,7 +40830,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39541,7 +41017,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39602,7 +41082,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39785,7 +41269,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39968,7 +41456,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40029,7 +41521,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40090,7 +41586,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40334,7 +41834,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40395,7 +41899,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40517,7 +42025,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40578,7 +42090,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40639,7 +42155,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40700,7 +42220,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40883,7 +42407,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40944,7 +42472,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41005,7 +42537,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41066,7 +42602,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41188,7 +42728,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41310,7 +42854,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41371,7 +42919,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41432,7 +42984,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41493,7 +43049,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41554,7 +43114,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41615,7 +43179,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41676,7 +43244,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41737,7 +43309,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41859,7 +43435,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41920,7 +43500,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41981,7 +43565,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42164,7 +43752,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42286,7 +43878,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42347,7 +43943,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42408,7 +44008,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/sep-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/sep-2025.xlsx
@@ -940,7 +940,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1196,7 +1200,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1822,7 +1830,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1944,7 +1956,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3208,7 +3224,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3456,7 +3476,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4021,7 +4045,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4212,7 +4240,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4338,7 +4370,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5350,7 +5386,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5602,7 +5642,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6179,7 +6223,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7626,7 +7674,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8121,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8565,7 +8621,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11735,7 +11795,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12820,7 +12884,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13129,7 +13197,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +14481,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15612,7 +15688,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16169,7 +16249,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16356,7 +16440,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16998,7 +17086,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17429,7 +17521,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17925,7 +18021,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22448,7 +22548,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22509,7 +22613,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23590,7 +23698,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24606,7 +24718,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24667,7 +24783,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24728,7 +24848,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24854,7 +24978,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25171,7 +25299,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25679,7 +25811,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26065,7 +26201,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26126,7 +26266,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26443,7 +26587,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26504,7 +26652,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26886,7 +27038,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27333,7 +27489,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27780,7 +27940,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28288,7 +28452,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28540,7 +28708,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29747,7 +29919,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29938,7 +30114,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31015,7 +31195,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31259,7 +31443,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31442,7 +31630,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31755,7 +31947,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31881,7 +32077,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34067,7 +34267,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34254,7 +34458,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35006,7 +35214,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35254,7 +35466,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36262,7 +36478,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36510,7 +36730,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36827,7 +37051,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38416,7 +38644,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38985,7 +39217,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39818,7 +40054,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40704,7 +40944,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40895,7 +41139,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40956,7 +41204,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42346,7 +42598,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
